--- a/data/merged/2026-08-31/MERGED_ES_Spot-Cleaner_2026-08-31.xlsx
+++ b/data/merged/2026-08-31/MERGED_ES_Spot-Cleaner_2026-08-31.xlsx
@@ -4433,13 +4433,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4521,13 +4521,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4653,13 +4653,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4697,13 +4697,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4785,13 +4785,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4829,7 +4829,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -4879,7 +4879,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4961,13 +4961,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5005,13 +5005,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5093,13 +5093,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5137,13 +5137,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5269,13 +5269,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5313,13 +5313,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5468,50 +5468,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5853,7 +5809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -8934,7 +8890,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0DDPL3PD2</t>
+          <t>B0DGLN5J2H</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -8947,23 +8903,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Clean &amp; Restore Carpet Cleaner Formula – CCS04</t>
+          <t>Ufesa Eden 600 Aspiradora de Tapicerías con Agua 600W, Doble Depósito, Succión de Líquidos y Sólidos, Cepillo Multifunción, A</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DDPL3PD2?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DGLN5J2H?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61chaSQ+1CL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71+6DQi1EBL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0DDPL3PD2</t>
+          <t>B0DGLN5J2H</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -8979,16 +8935,18 @@
       <c r="W27" s="15"/>
       <c r="X27" s="15"/>
       <c r="Y27"/>
-      <c r="Z27" s="4"/>
+      <c r="Z27" s="4">
+        <v>61.02</v>
+      </c>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="19">
-        <v>635</v>
+        <v>372</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="20">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG27" s="21">
         <v>0</v>
@@ -9040,7 +8998,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0DGLN5J2H</t>
+          <t>B0DLKT9PK9</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -9053,23 +9011,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Ufesa Eden 600 Aspiradora de Tapicerías con Agua 600W, Doble Depósito, Succión de Líquidos y Sólidos, Cepillo Multifunción, A</t>
+          <t>Cecotec Limpiador Aspirador de Tapicerías Conga Rockstar 4000 Mattress. ForceSonic 400W, 13 kPa, UV-C Light, Heat Tech, Cepil</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DGLN5J2H?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DLKT9PK9?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71+6DQi1EBL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71RtzAuhKWL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0DGLN5J2H</t>
+          <t>B0DLKT9PK9</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -9086,17 +9044,17 @@
       <c r="X28" s="15"/>
       <c r="Y28"/>
       <c r="Z28" s="4">
-        <v>61.02</v>
+        <v>41.24</v>
       </c>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28"/>
       <c r="AD28" s="19">
-        <v>372</v>
+        <v>104</v>
       </c>
       <c r="AE28"/>
       <c r="AF28" s="20">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG28" s="21">
         <v>0</v>
@@ -9148,7 +9106,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0DLKT9PK9</t>
+          <t>B0DN68M1FK</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -9161,23 +9119,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Limpiador Aspirador de Tapicerías Conga Rockstar 4000 Mattress. ForceSonic 400W, 13 kPa, UV-C Light, Heat Tech, Cepil</t>
+          <t>BISSELL PowerWash Compact Pet Aspiradora de Agua 4058NsLimpiador para tapicería y alfombras, manchas y olores de mascotas,</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DLKT9PK9?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DN68M1FK?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71RtzAuhKWL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/617VZB4pynL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0DLKT9PK9</t>
+          <t>B0DN68M1FK</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -9194,13 +9152,13 @@
       <c r="X29" s="15"/>
       <c r="Y29"/>
       <c r="Z29" s="4">
-        <v>41.24</v>
+        <v>148.75</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="19">
-        <v>104</v>
+        <v>208</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="20">
@@ -9256,7 +9214,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0DN68M1FK</t>
+          <t>B0DPLBZL99</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -9269,23 +9227,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>BISSELL PowerWash Compact Pet Aspiradora de Agua 4058NsLimpiador para tapicería y alfombras, manchas y olores de mascotas,</t>
+          <t>Rowenta Clean It Solución limpiadora de tejidos y alfombrassCantidad de 1L, Fórmula diluible elimina manchas cotidianas y d</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DN68M1FK?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DPLBZL99?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/617VZB4pynL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61XbFdIUl+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0DN68M1FK</t>
+          <t>B0DPLBZL99</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -9302,17 +9260,17 @@
       <c r="X30" s="15"/>
       <c r="Y30"/>
       <c r="Z30" s="4">
-        <v>148.75</v>
+        <v>14.87</v>
       </c>
       <c r="AA30"/>
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="19">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="20">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AG30" s="21">
         <v>0</v>
@@ -9364,7 +9322,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0DPLBZL99</t>
+          <t>B0DSC6DRWW</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -9377,23 +9335,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Rowenta Clean It Solución limpiadora de tejidos y alfombrassCantidad de 1L, Fórmula diluible elimina manchas cotidianas y d</t>
+          <t>CLEANmaxx Limpiador de tapicería Pro Power, 600 W, color azul, potente aspiradora de lavado con doble depósito y autolimpieza</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DPLBZL99?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DSC6DRWW?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61XbFdIUl+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71l5561XnIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0DPLBZL99</t>
+          <t>B0DSC6DRWW</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -9409,18 +9367,16 @@
       <c r="W31" s="15"/>
       <c r="X31" s="15"/>
       <c r="Y31"/>
-      <c r="Z31" s="4">
-        <v>14.87</v>
-      </c>
+      <c r="Z31" s="4"/>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="19">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="20">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AG31" s="21">
         <v>0</v>
@@ -9472,7 +9428,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0DSC6DRWW</t>
+          <t>B0F8J7LK2X</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -9485,23 +9441,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>CLEANmaxx Limpiador de tapicería Pro Power, 600 W, color azul, potente aspiradora de lavado con doble depósito y autolimpieza</t>
+          <t>Cecotec Limpiador Aspirador de Tapicerias y Alfombras Conga 7000 Carpet&amp;Spot Clean Steam XXL Essential. 1700W, Limpieza Vapor</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DSC6DRWW?psc=1</t>
+          <t>https://www.amazon.es/dp/B0F8J7LK2X?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71l5561XnIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71OxeiwQetL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0DSC6DRWW</t>
+          <t>B0F8J7LK2X</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -9517,12 +9473,14 @@
       <c r="W32" s="15"/>
       <c r="X32" s="15"/>
       <c r="Y32"/>
-      <c r="Z32" s="4"/>
+      <c r="Z32" s="4">
+        <v>106.61</v>
+      </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="19">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="20">
@@ -9578,7 +9536,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0F8J7LK2X</t>
+          <t>B0F9PL9GM3</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -9591,23 +9549,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Limpiador Aspirador de Tapicerias y Alfombras Conga 7000 Carpet&amp;Spot Clean Steam XXL Essential. 1700W, Limpieza Vapor</t>
+          <t>Vax SpotWash Duo Quitamanchas para alfombras y tapicería con herramienta para mascotas, accesorios multi-superficie y solució</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0F8J7LK2X?psc=1</t>
+          <t>https://www.amazon.es/dp/B0F9PL9GM3?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71OxeiwQetL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71pw+OV+LtL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0F8J7LK2X</t>
+          <t>B0F9PL9GM3</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -9623,18 +9581,16 @@
       <c r="W33" s="15"/>
       <c r="X33" s="15"/>
       <c r="Y33"/>
-      <c r="Z33" s="4">
-        <v>106.61</v>
-      </c>
+      <c r="Z33" s="4"/>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33" s="19">
-        <v>59</v>
+        <v>253</v>
       </c>
       <c r="AE33"/>
       <c r="AF33" s="20">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AG33" s="21">
         <v>0</v>
@@ -9686,7 +9642,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0F9PL9GM3</t>
+          <t>B0FH4QL9GN</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -9699,23 +9655,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Vax SpotWash Duo Quitamanchas para alfombras y tapicería con herramienta para mascotas, accesorios multi-superficie y solució</t>
+          <t>Livatro Limpia Tapicerías con Gran Depósito para Sofás y AlfombrassAgua limpia de 2,3 L y agua sucia de 1,3 L para limpiar</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0F9PL9GM3?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FH4QL9GN?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71pw+OV+LtL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71nARwekliL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0F9PL9GM3</t>
+          <t>B0FH4QL9GN</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -9736,11 +9692,11 @@
       <c r="AB34"/>
       <c r="AC34"/>
       <c r="AD34" s="19">
-        <v>253</v>
+        <v>508</v>
       </c>
       <c r="AE34"/>
       <c r="AF34" s="20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG34" s="21">
         <v>0</v>
@@ -9792,7 +9748,7 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
+          <t>B0FJFDG5PY</t>
         </is>
       </c>
       <c r="D35" s="14"/>
@@ -9805,23 +9761,23 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Livatro Limpia Tapicerías con Gran Depósito para Sofás y AlfombrassAgua limpia de 2,3 L y agua sucia de 1,3 L para limpiar</t>
+          <t>Akitas X7 600W Aspiradora de Agua Tapicería con Función de Autolimpieza Limpiador de Tapicerías Portátil 14kPa Pelos de Masco</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FH4QL9GN?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FJFDG5PY?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71nARwekliL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71XUjnFFERL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
+          <t>B0FJFDG5PY</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -9842,11 +9798,11 @@
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35" s="19">
-        <v>508</v>
+        <v>2750</v>
       </c>
       <c r="AE35"/>
       <c r="AF35" s="20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG35" s="21">
         <v>0</v>
@@ -9898,7 +9854,7 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0FJFDG5PY</t>
+          <t>B0FL7GZKJW</t>
         </is>
       </c>
       <c r="D36" s="14"/>
@@ -9911,23 +9867,23 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Akitas X7 600W Aspiradora de Agua Tapicería con Función de Autolimpieza Limpiador de Tapicerías Portátil 14kPa Pelos de Masco</t>
+          <t>Cecotec Limpiador Aspirador de Tapicerias y Alfombras con Cable Compacto Conga 3000 Carpet&amp;Spot Clean X-Treme. 450W, 13kPa, D</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FJFDG5PY?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FL7GZKJW?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71XUjnFFERL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71J-puz9iAL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0FJFDG5PY</t>
+          <t>B0FL7GZKJW</t>
         </is>
       </c>
       <c r="M36" s="1"/>
@@ -9948,11 +9904,11 @@
       <c r="AB36"/>
       <c r="AC36"/>
       <c r="AD36" s="19">
-        <v>2750</v>
+        <v>90</v>
       </c>
       <c r="AE36"/>
       <c r="AF36" s="20">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG36" s="21">
         <v>0</v>
@@ -10004,7 +9960,7 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0FL7GZKJW</t>
+          <t>B0G8ZCQP4L</t>
         </is>
       </c>
       <c r="D37" s="14"/>
@@ -10017,23 +9973,23 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Limpiador Aspirador de Tapicerias y Alfombras con Cable Compacto Conga 3000 Carpet&amp;Spot Clean X-Treme. 450W, 13kPa, D</t>
+          <t>ICARE Limpia Tapicerias 600W - 22kPa Aspiradora de Agua Tapiceria con det.sLimpiador de Alfombras Portátil con Líquido Limp</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FL7GZKJW?psc=1</t>
+          <t>https://www.amazon.es/dp/B0G8ZCQP4L?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71J-puz9iAL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71ZssJeybXL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0FL7GZKJW</t>
+          <t>B0G8ZCQP4L</t>
         </is>
       </c>
       <c r="M37" s="1"/>
@@ -10054,11 +10010,11 @@
       <c r="AB37"/>
       <c r="AC37"/>
       <c r="AD37" s="19">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="AE37"/>
       <c r="AF37" s="20">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AG37" s="21">
         <v>0</v>
@@ -10110,7 +10066,7 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0G8ZCQP4L</t>
+          <t>B0GDCZ7BWK</t>
         </is>
       </c>
       <c r="D38" s="14"/>
@@ -10123,23 +10079,23 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>ICARE Limpia Tapicerias 600W - 22kPa Aspiradora de Agua Tapiceria con det.sLimpiador de Alfombras Portátil con Líquido Limp</t>
+          <t>HYCHIKA Limpiador de Tapicerías 1800W, 17 kPa, Aspirador de Tapicerías con Lavado, Doble Depósito y Autolimpieza, Limpiador d</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0G8ZCQP4L?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GDCZ7BWK?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71ZssJeybXL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81+UtbT-JGL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0G8ZCQP4L</t>
+          <t>B0GDCZ7BWK</t>
         </is>
       </c>
       <c r="M38" s="1"/>
@@ -10155,16 +10111,18 @@
       <c r="W38" s="15"/>
       <c r="X38" s="15"/>
       <c r="Y38"/>
-      <c r="Z38" s="4"/>
+      <c r="Z38" s="4">
+        <v>94.62</v>
+      </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38"/>
       <c r="AD38" s="19">
-        <v>12</v>
+        <v>195</v>
       </c>
       <c r="AE38"/>
       <c r="AF38" s="20">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AG38" s="21">
         <v>0</v>
@@ -10216,7 +10174,7 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0GDCZ7BWK</t>
+          <t>B0GFF7C519</t>
         </is>
       </c>
       <c r="D39" s="14"/>
@@ -10229,23 +10187,23 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>HYCHIKA Limpiador de Tapicerías 1800W, 17 kPa, Aspirador de Tapicerías con Lavado, Doble Depósito y Autolimpieza, Limpiador d</t>
+          <t>Akitas X5 Aspiradora de Agua Tapicería con Función Autolimpieza, 30ml Solución Concentrada, Portátil para Mascotas, Sofás, Co</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GDCZ7BWK?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GFF7C519?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81+UtbT-JGL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71y7DHT1x-L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0GDCZ7BWK</t>
+          <t>B0GFF7C519</t>
         </is>
       </c>
       <c r="M39" s="1"/>
@@ -10261,18 +10219,16 @@
       <c r="W39" s="15"/>
       <c r="X39" s="15"/>
       <c r="Y39"/>
-      <c r="Z39" s="4">
-        <v>94.62</v>
-      </c>
+      <c r="Z39" s="4"/>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39"/>
       <c r="AD39" s="19">
-        <v>195</v>
+        <v>328</v>
       </c>
       <c r="AE39"/>
       <c r="AF39" s="20">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG39" s="21">
         <v>0</v>
@@ -10324,7 +10280,7 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0GFF7C519</t>
+          <t>B0GFKK2WXT</t>
         </is>
       </c>
       <c r="D40" s="14"/>
@@ -10337,23 +10293,23 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Akitas X5 Aspiradora de Agua Tapicería con Función Autolimpieza, 30ml Solución Concentrada, Portátil para Mascotas, Sofás, Co</t>
+          <t>Vacmaster Limpiador alfombras calefactor 1150W 17KPA autolimpieza sofásTecnología de calefacción, autolimpieza, sofá, escal</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GFF7C519?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GFKK2WXT?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71y7DHT1x-L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71xLT6M5eiL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0GFF7C519</t>
+          <t>B0GFKK2WXT</t>
         </is>
       </c>
       <c r="M40" s="1"/>
@@ -10369,16 +10325,18 @@
       <c r="W40" s="15"/>
       <c r="X40" s="15"/>
       <c r="Y40"/>
-      <c r="Z40" s="4"/>
+      <c r="Z40" s="4">
+        <v>90.9</v>
+      </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40"/>
       <c r="AD40" s="19">
-        <v>328</v>
+        <v>23</v>
       </c>
       <c r="AE40"/>
       <c r="AF40" s="20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG40" s="21">
         <v>0</v>
@@ -10430,7 +10388,7 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0GFKK2WXT</t>
+          <t>B0GQGRY9FW</t>
         </is>
       </c>
       <c r="D41" s="14"/>
@@ -10443,23 +10401,23 @@
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Limpiador alfombras calefactor 1150W 17KPA autolimpieza sofásTecnología de calefacción, autolimpieza, sofá, escal</t>
+          <t>X-cotec Limpiador de Tapicerías 450W 13kPa, Aspiradora de Agua para Tapicería y Sofá, Máquina para Limpiar Sofás, Alfombras y</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GFKK2WXT?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GQGRY9FW?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71xLT6M5eiL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81ePoJNjBiL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0GFKK2WXT</t>
+          <t>B0GQGRY9FW</t>
         </is>
       </c>
       <c r="M41" s="1"/>
@@ -10475,18 +10433,16 @@
       <c r="W41" s="15"/>
       <c r="X41" s="15"/>
       <c r="Y41"/>
-      <c r="Z41" s="4">
-        <v>90.9</v>
-      </c>
+      <c r="Z41" s="4"/>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41"/>
       <c r="AD41" s="19">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="AE41"/>
       <c r="AF41" s="20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG41" s="21">
         <v>0</v>
@@ -10538,7 +10494,7 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0GQGRY9FW</t>
+          <t>B0GQVX8HWW</t>
         </is>
       </c>
       <c r="D42" s="14"/>
@@ -10551,23 +10507,23 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>X-cotec Limpiador de Tapicerías 450W 13kPa, Aspiradora de Agua para Tapicería y Sofá, Máquina para Limpiar Sofás, Alfombras y</t>
+          <t>Rowenta Clean It Hot &amp; Cold, Aspiradora tapicerías 1150W, 5 Acc, NegrosTecnología Powerheat, Limpieza 3 en 1 para tapicería</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GQGRY9FW?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GQVX8HWW?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81ePoJNjBiL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81ZoJC+ypoL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0GQGRY9FW</t>
+          <t>B0GQVX8HWW</t>
         </is>
       </c>
       <c r="M42" s="1"/>
@@ -10583,16 +10539,18 @@
       <c r="W42" s="15"/>
       <c r="X42" s="15"/>
       <c r="Y42"/>
-      <c r="Z42" s="4"/>
+      <c r="Z42" s="4">
+        <v>135.53</v>
+      </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42"/>
       <c r="AD42" s="19">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="AE42"/>
       <c r="AF42" s="20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG42" s="21">
         <v>0</v>
@@ -10644,7 +10602,7 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0GQVX8HWW</t>
+          <t>B0GTQ7NRR5</t>
         </is>
       </c>
       <c r="D43" s="14"/>
@@ -10657,23 +10615,23 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Rowenta Clean It Hot &amp; Cold, Aspiradora tapicerías 1150W, 5 Acc, NegrosTecnología Powerheat, Limpieza 3 en 1 para tapicería</t>
+          <t>Redkey C2 Aspiradora de Agua Tapicería Lava y Aspira con Vapor, 1800W 26000Pa Aspirador de Alfombras, Limpiador de Tapicerías</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GQVX8HWW?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GTQ7NRR5?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81ZoJC+ypoL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/710LGMIAr9L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0GQVX8HWW</t>
+          <t>B0GTQ7NRR5</t>
         </is>
       </c>
       <c r="M43" s="1"/>
@@ -10690,17 +10648,17 @@
       <c r="X43" s="15"/>
       <c r="Y43"/>
       <c r="Z43" s="4">
-        <v>135.53</v>
+        <v>109.9</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43"/>
       <c r="AD43" s="19">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="AE43"/>
       <c r="AF43" s="20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG43" s="21">
         <v>0</v>
@@ -10752,7 +10710,7 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0GTQ7NRR5</t>
+          <t>B0GV373WYL</t>
         </is>
       </c>
       <c r="D44" s="14"/>
@@ -10765,23 +10723,23 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Redkey C2 Aspiradora de Agua Tapicería Lava y Aspira con Vapor, 1800W 26000Pa Aspirador de Alfombras, Limpiador de Tapicerías</t>
+          <t>Vacmaster Limpiador de alfombras con doble rodillo de cepillo 17kpa, gran superficie de limpieza – ideal para alfombras, esca</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GTQ7NRR5?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GV373WYL?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/710LGMIAr9L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61UlWbltxeL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0GTQ7NRR5</t>
+          <t>B0GV373WYL</t>
         </is>
       </c>
       <c r="M44" s="1"/>
@@ -10798,17 +10756,17 @@
       <c r="X44" s="15"/>
       <c r="Y44"/>
       <c r="Z44" s="4">
-        <v>109.9</v>
+        <v>140.49</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44"/>
       <c r="AD44" s="19">
-        <v>99</v>
+        <v>255</v>
       </c>
       <c r="AE44"/>
       <c r="AF44" s="20">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG44" s="21">
         <v>0</v>
@@ -10860,7 +10818,7 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0GV373WYL</t>
+          <t>B0GYF1F5HN</t>
         </is>
       </c>
       <c r="D45" s="14"/>
@@ -10873,23 +10831,23 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Limpiador de alfombras con doble rodillo de cepillo 17kpa, gran superficie de limpieza – ideal para alfombras, esca</t>
+          <t>Uwant Máquina Limpiadora de Alfombras 22Kpa Aspiradora Portátil para Mascotas, Limpiador de Tapicerías con Solución Oxy Set d</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GV373WYL?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GYF1F5HN?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61UlWbltxeL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71OW8kkanHL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0GV373WYL</t>
+          <t>B0GYF1F5HN</t>
         </is>
       </c>
       <c r="M45" s="1"/>
@@ -10905,18 +10863,16 @@
       <c r="W45" s="15"/>
       <c r="X45" s="15"/>
       <c r="Y45"/>
-      <c r="Z45" s="4">
-        <v>140.49</v>
-      </c>
+      <c r="Z45" s="4"/>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45"/>
       <c r="AD45" s="19">
-        <v>255</v>
+        <v>8</v>
       </c>
       <c r="AE45"/>
       <c r="AF45" s="20">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AG45" s="21">
         <v>0</v>
@@ -10968,7 +10924,7 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0GYF1F5HN</t>
+          <t>B0GYNKF8T9</t>
         </is>
       </c>
       <c r="D46" s="14"/>
@@ -10981,23 +10937,23 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Uwant Máquina Limpiadora de Alfombras 22Kpa Aspiradora Portátil para Mascotas, Limpiador de Tapicerías con Solución Oxy Set d</t>
+          <t>Cecotec Aspirador Limpiatapicerías de Trineo Conga CarpetClean 30000 Steam. Potencia de 2200 W, Succión de 18 kPa, Vapor y Ag</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GYF1F5HN?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GYNKF8T9?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71OW8kkanHL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71LzKewJeSL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0GYF1F5HN</t>
+          <t>B0GYNKF8T9</t>
         </is>
       </c>
       <c r="M46" s="1"/>
@@ -11013,16 +10969,18 @@
       <c r="W46" s="15"/>
       <c r="X46" s="15"/>
       <c r="Y46"/>
-      <c r="Z46" s="4"/>
+      <c r="Z46" s="4">
+        <v>123.14</v>
+      </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46"/>
       <c r="AD46" s="19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE46"/>
       <c r="AF46" s="20">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AG46" s="21">
         <v>0</v>
@@ -11074,7 +11032,7 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0GYNKF8T9</t>
+          <t>B0H1B164KH</t>
         </is>
       </c>
       <c r="D47" s="14"/>
@@ -11087,23 +11045,23 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Aspirador Limpiatapicerías de Trineo Conga CarpetClean 30000 Steam. Potencia de 2200 W, Succión de 18 kPa, Vapor y Ag</t>
+          <t>Uwant Y100S Limpiador Tapicerias Vapor 3en1, 1750W 18kPa Aspiradora de Aguas2 dep. 1.2L, Manguera Autolimpiable, Cepillo 2e</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GYNKF8T9?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H1B164KH?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71LzKewJeSL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0GYNKF8T9</t>
+          <t>B0H1B164KH</t>
         </is>
       </c>
       <c r="M47" s="1"/>
@@ -11119,18 +11077,16 @@
       <c r="W47" s="15"/>
       <c r="X47" s="15"/>
       <c r="Y47"/>
-      <c r="Z47" s="4">
-        <v>123.14</v>
-      </c>
+      <c r="Z47" s="4"/>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47"/>
       <c r="AD47" s="19">
-        <v>7</v>
+        <v>334</v>
       </c>
       <c r="AE47"/>
       <c r="AF47" s="20">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AG47" s="21">
         <v>0</v>
@@ -11182,7 +11138,7 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0H1B164KH</t>
+          <t>B0H2W1SXP6</t>
         </is>
       </c>
       <c r="D48" s="14"/>
@@ -11195,23 +11151,23 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Uwant Y100S Limpiador Tapicerias Vapor 3en1, 1750W 18kPa Aspiradora de Aguas2 dep. 1.2L, Manguera Autolimpiable, Cepillo 2e</t>
+          <t>Pack de 2 Limpiador de Tapicerías para Máquinas de Inyección – Calidad Profesional – Elimina Manchas y Olores en Tapicerías,</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0H1B164KH?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H2W1SXP6?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71ehipu+P3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0H1B164KH</t>
+          <t>B0H2W1SXP6</t>
         </is>
       </c>
       <c r="M48" s="1"/>
@@ -11232,7 +11188,7 @@
       <c r="AB48"/>
       <c r="AC48"/>
       <c r="AD48" s="19">
-        <v>334</v>
+        <v>117</v>
       </c>
       <c r="AE48"/>
       <c r="AF48" s="20">
@@ -11288,7 +11244,7 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0H2W1SXP6</t>
+          <t>B0H97LW9DL</t>
         </is>
       </c>
       <c r="D49" s="14"/>
@@ -11301,23 +11257,23 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Pack de 2 Limpiador de Tapicerías para Máquinas de Inyección – Calidad Profesional – Elimina Manchas y Olores en Tapicerías,</t>
+          <t>PUREBEAR Limpiador de manchas portátil con boquilla de autolimpiezasSofás, Alfombras y Colchones| Motor 500W Succión 18kPa|</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0H2W1SXP6?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H97LW9DL?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71ehipu+P3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51LnggCx6eL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0H2W1SXP6</t>
+          <t>B0H97LW9DL</t>
         </is>
       </c>
       <c r="M49" s="1"/>
@@ -11338,11 +11294,11 @@
       <c r="AB49"/>
       <c r="AC49"/>
       <c r="AD49" s="19">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="AE49"/>
       <c r="AF49" s="20">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AG49" s="21">
         <v>0</v>
@@ -11394,7 +11350,7 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0H97LW9DL</t>
+          <t>B0HF7YZWZZ</t>
         </is>
       </c>
       <c r="D50" s="14"/>
@@ -11407,23 +11363,23 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>PUREBEAR Limpiador de manchas portátil con boquilla de autolimpiezasSofás, Alfombras y Colchones| Motor 500W Succión 18kPa|</t>
+          <t>Aspiradora Agua Tapiceria Limpiador, con calentamiento instantáneo, 600W potente succión y limpieza profunda para alfombras,</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0H97LW9DL?psc=1</t>
+          <t>https://www.amazon.es/dp/B0HF7YZWZZ?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51LnggCx6eL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71q5d5+bbdL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0H97LW9DL</t>
+          <t>B0HF7YZWZZ</t>
         </is>
       </c>
       <c r="M50" s="1"/>
@@ -11444,7 +11400,7 @@
       <c r="AB50"/>
       <c r="AC50"/>
       <c r="AD50" s="19">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="AE50"/>
       <c r="AF50" s="20">
@@ -11492,112 +11448,6 @@
       <c r="BP50"/>
       <c r="BQ50" s="22"/>
       <c r="BR50"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HF7YZWZZ</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.esundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Aspiradora Agua Tapiceria Limpiador, con calentamiento instantáneo, 600W potente succión y limpieza profunda para alfombras,</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0HF7YZWZZ?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71q5d5+bbdL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HF7YZWZZ</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="19">
-        <v>4</v>
-      </c>
-      <c r="AE51"/>
-      <c r="AF51" s="20">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="22"/>
-      <c r="BL51"/>
-      <c r="BM51" s="22"/>
-      <c r="BN51"/>
-      <c r="BO51" s="22"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="22"/>
-      <c r="BR51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11728,133 +11578,128 @@
     <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.es/dp/B0DDKZBYK6?psc=1"/>
     <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TGCJz8hSL._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.es/dp/B0DDKZBYK6"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.es/dp/B0DDPL3PD2"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.es/dp/B0DGLN5J2H"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.es/dp/B0DDPL3PD2?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61chaSQ+1CL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.es/dp/B0DDPL3PD2"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.es/dp/B0DGLN5J2H"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.es/dp/B0DGLN5J2H?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+6DQi1EBL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.es/dp/B0DGLN5J2H"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.es/dp/B0DLKT9PK9"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.es/dp/B0DGLN5J2H?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+6DQi1EBL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.es/dp/B0DGLN5J2H"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.es/dp/B0DLKT9PK9"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.es/dp/B0DLKT9PK9?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RtzAuhKWL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.es/dp/B0DLKT9PK9"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.es/dp/B0DN68M1FK"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.es/dp/B0DLKT9PK9?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RtzAuhKWL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.es/dp/B0DLKT9PK9"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.es/dp/B0DN68M1FK"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.es/dp/B0DN68M1FK?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/617VZB4pynL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.es/dp/B0DN68M1FK"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.es/dp/B0DPLBZL99"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.es/dp/B0DN68M1FK?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/617VZB4pynL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.es/dp/B0DN68M1FK"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.es/dp/B0DPLBZL99"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.es/dp/B0DPLBZL99?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61XbFdIUl+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.es/dp/B0DPLBZL99"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.es/dp/B0DSC6DRWW"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.es/dp/B0DPLBZL99?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61XbFdIUl+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.es/dp/B0DPLBZL99"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.es/dp/B0DSC6DRWW"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.es/dp/B0DSC6DRWW?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71l5561XnIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.es/dp/B0DSC6DRWW"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.es/dp/B0F8J7LK2X"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.es/dp/B0DSC6DRWW?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71l5561XnIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.es/dp/B0DSC6DRWW"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.es/dp/B0F8J7LK2X"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.es/dp/B0F8J7LK2X?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71OxeiwQetL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.es/dp/B0F8J7LK2X"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.es/dp/B0F9PL9GM3"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.es/dp/B0F8J7LK2X?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71OxeiwQetL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.es/dp/B0F8J7LK2X"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.es/dp/B0F9PL9GM3"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.es/dp/B0F9PL9GM3?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pw+OV+LtL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.es/dp/B0F9PL9GM3"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.es/dp/B0FH4QL9GN"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.es/dp/B0F9PL9GM3?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pw+OV+LtL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.es/dp/B0F9PL9GM3"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.es/dp/B0FH4QL9GN"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.es/dp/B0FH4QL9GN?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71nARwekliL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.es/dp/B0FH4QL9GN"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.es/dp/B0FJFDG5PY"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.es/dp/B0FH4QL9GN?psc=1"/>
-    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71nARwekliL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.es/dp/B0FH4QL9GN"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.es/dp/B0FJFDG5PY"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.es/dp/B0FJFDG5PY?psc=1"/>
+    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71XUjnFFERL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.es/dp/B0FJFDG5PY"/>
+    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.es/dp/B0FL7GZKJW"/>
     <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.es/dp/B0FJFDG5PY?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71XUjnFFERL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.es/dp/B0FJFDG5PY"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.es/dp/B0FL7GZKJW"/>
+    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.es/dp/B0FL7GZKJW?psc=1"/>
+    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71J-puz9iAL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.es/dp/B0FL7GZKJW"/>
+    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.es/dp/B0G8ZCQP4L"/>
     <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.es/dp/B0FL7GZKJW?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71J-puz9iAL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.es/dp/B0FL7GZKJW"/>
-    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.es/dp/B0G8ZCQP4L"/>
+    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.es/dp/B0G8ZCQP4L?psc=1"/>
+    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ZssJeybXL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.es/dp/B0G8ZCQP4L"/>
+    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.es/dp/B0GDCZ7BWK"/>
     <hyperlink ref="G38" r:id="rId182" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.es/dp/B0G8ZCQP4L?psc=1"/>
-    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ZssJeybXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.es/dp/B0G8ZCQP4L"/>
-    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.es/dp/B0GDCZ7BWK"/>
+    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.es/dp/B0GDCZ7BWK?psc=1"/>
+    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81+UtbT-JGL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.es/dp/B0GDCZ7BWK"/>
+    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.es/dp/B0GFF7C519"/>
     <hyperlink ref="G39" r:id="rId187" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.es/dp/B0GDCZ7BWK?psc=1"/>
-    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81+UtbT-JGL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.es/dp/B0GDCZ7BWK"/>
-    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.es/dp/B0GFF7C519"/>
+    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.es/dp/B0GFF7C519?psc=1"/>
+    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71y7DHT1x-L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.es/dp/B0GFF7C519"/>
+    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.es/dp/B0GFKK2WXT"/>
     <hyperlink ref="G40" r:id="rId192" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.es/dp/B0GFF7C519?psc=1"/>
-    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71y7DHT1x-L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.es/dp/B0GFF7C519"/>
-    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.es/dp/B0GFKK2WXT"/>
+    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.es/dp/B0GFKK2WXT?psc=1"/>
+    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xLT6M5eiL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.es/dp/B0GFKK2WXT"/>
+    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.es/dp/B0GQGRY9FW"/>
     <hyperlink ref="G41" r:id="rId197" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.es/dp/B0GFKK2WXT?psc=1"/>
-    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xLT6M5eiL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.es/dp/B0GFKK2WXT"/>
-    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.es/dp/B0GQGRY9FW"/>
+    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.es/dp/B0GQGRY9FW?psc=1"/>
+    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81ePoJNjBiL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.es/dp/B0GQGRY9FW"/>
+    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.es/dp/B0GQVX8HWW"/>
     <hyperlink ref="G42" r:id="rId202" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.es/dp/B0GQGRY9FW?psc=1"/>
-    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81ePoJNjBiL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.es/dp/B0GQGRY9FW"/>
-    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.es/dp/B0GQVX8HWW"/>
+    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.es/dp/B0GQVX8HWW?psc=1"/>
+    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81ZoJC+ypoL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.es/dp/B0GQVX8HWW"/>
+    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.es/dp/B0GTQ7NRR5"/>
     <hyperlink ref="G43" r:id="rId207" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.es/dp/B0GQVX8HWW?psc=1"/>
-    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81ZoJC+ypoL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.es/dp/B0GQVX8HWW"/>
-    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.es/dp/B0GTQ7NRR5"/>
+    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.es/dp/B0GTQ7NRR5?psc=1"/>
+    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/710LGMIAr9L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.es/dp/B0GTQ7NRR5"/>
+    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.es/dp/B0GV373WYL"/>
     <hyperlink ref="G44" r:id="rId212" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.es/dp/B0GTQ7NRR5?psc=1"/>
-    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/710LGMIAr9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.es/dp/B0GTQ7NRR5"/>
-    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.es/dp/B0GV373WYL"/>
+    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.es/dp/B0GV373WYL?psc=1"/>
+    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61UlWbltxeL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.es/dp/B0GV373WYL"/>
+    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.es/dp/B0GYF1F5HN"/>
     <hyperlink ref="G45" r:id="rId217" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.es/dp/B0GV373WYL?psc=1"/>
-    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61UlWbltxeL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.es/dp/B0GV373WYL"/>
-    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.es/dp/B0GYF1F5HN"/>
+    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.es/dp/B0GYF1F5HN?psc=1"/>
+    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71OW8kkanHL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.es/dp/B0GYF1F5HN"/>
+    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.es/dp/B0GYNKF8T9"/>
     <hyperlink ref="G46" r:id="rId222" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.es/dp/B0GYF1F5HN?psc=1"/>
-    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71OW8kkanHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.es/dp/B0GYF1F5HN"/>
-    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.es/dp/B0GYNKF8T9"/>
+    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.es/dp/B0GYNKF8T9?psc=1"/>
+    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71LzKewJeSL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.es/dp/B0GYNKF8T9"/>
+    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.es/dp/B0H1B164KH"/>
     <hyperlink ref="G47" r:id="rId227" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.es/dp/B0GYNKF8T9?psc=1"/>
-    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71LzKewJeSL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.es/dp/B0GYNKF8T9"/>
-    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.es/dp/B0H1B164KH"/>
+    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.es/dp/B0H1B164KH?psc=1"/>
+    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.es/dp/B0H1B164KH"/>
+    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.es/dp/B0H2W1SXP6"/>
     <hyperlink ref="G48" r:id="rId232" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.es/dp/B0H1B164KH?psc=1"/>
-    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.es/dp/B0H1B164KH"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.es/dp/B0H2W1SXP6"/>
+    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.es/dp/B0H2W1SXP6?psc=1"/>
+    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ehipu+P3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.es/dp/B0H2W1SXP6"/>
+    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.es/dp/B0H97LW9DL"/>
     <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.es/dp/B0H2W1SXP6?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ehipu+P3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.es/dp/B0H2W1SXP6"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.es/dp/B0H97LW9DL"/>
+    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.es/dp/B0H97LW9DL?psc=1"/>
+    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51LnggCx6eL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.es/dp/B0H97LW9DL"/>
+    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.es/dp/B0HF7YZWZZ"/>
     <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.es/dp/B0H97LW9DL?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51LnggCx6eL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.es/dp/B0H97LW9DL"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.es/dp/B0HF7YZWZZ"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.es/dp/B0HF7YZWZZ?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71q5d5+bbdL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.es/dp/B0HF7YZWZZ"/>
+    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.es/dp/B0HF7YZWZZ?psc=1"/>
+    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71q5d5+bbdL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.es/dp/B0HF7YZWZZ"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId246"/>
 </worksheet>
 </file>
 
